--- a/SPCX_DCF_Model.xlsx
+++ b/SPCX_DCF_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://srvusd-my.sharepoint.com/personal/252706_students_srvusd_net/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B6C63CB-4183-4243-851F-3902C4FDA9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91D1516F-E919-408F-B22A-CBD3756726E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="204">
   <si>
     <t>Space Exploration Technologies Corp. (NASDAQ: SPCX)</t>
   </si>
@@ -181,7 +181,7 @@
     <t>Prepared by</t>
   </si>
   <si>
-    <t>Aleem</t>
+    <t>Aleem Ahmad</t>
   </si>
   <si>
     <t>EV - Connectivity only</t>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>Live EV check</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Assumptions C3 selects the segment (1 = Connectivity, 2 = Space). C10 and C11 hold values from the two separate runs.</t>
   </si>
   <si>
     <t>SPCX - DCF Assumptions</t>
@@ -1914,6 +1917,9 @@
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1">
       <c r="A31" s="24"/>
+      <c r="B31" s="20" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1">
       <c r="B32" s="3"/>
@@ -1965,17 +1971,17 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1">
       <c r="A3" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="37">
         <v>1</v>
@@ -1984,31 +1990,31 @@
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="38"/>
       <c r="C4" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H4" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
       <c r="A5" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="40">
@@ -2034,7 +2040,7 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" s="40">
         <f t="shared" ref="C6:H8" si="0">IF(CHOOSE($C$3,C23,C31)="","",CHOOSE($C$3,C23,C31))</f>
@@ -2063,7 +2069,7 @@
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" s="40">
         <f t="shared" si="0"/>
@@ -2092,7 +2098,7 @@
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="40">
         <f t="shared" si="0"/>
@@ -2121,16 +2127,16 @@
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" s="38"/>
       <c r="C10" s="38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" s="41">
         <f>CHOOSE($C$3,'Revenue Build'!C17,'Revenue Build'!C25)</f>
@@ -2140,7 +2146,7 @@
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="42">
         <v>0.2</v>
@@ -2149,7 +2155,7 @@
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" s="42">
         <v>0.09</v>
@@ -2158,7 +2164,7 @@
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" s="42">
         <v>2.5000000000000001E-2</v>
@@ -2167,7 +2173,7 @@
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C15" s="43">
         <f>CHOOSE($C$3,C27,C35)</f>
@@ -2177,7 +2183,7 @@
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C16" s="44">
         <f>93.522+6.487-39.364</f>
@@ -2187,7 +2193,7 @@
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" s="44">
         <v>13.176</v>
@@ -2196,7 +2202,7 @@
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C18" s="45">
         <v>151.97</v>
@@ -2208,31 +2214,31 @@
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="40">
@@ -2257,7 +2263,7 @@
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="40">
@@ -2282,7 +2288,7 @@
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="40">
@@ -2307,7 +2313,7 @@
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="47">
@@ -2321,7 +2327,7 @@
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="48">
@@ -2355,31 +2361,31 @@
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D30" s="50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F30" s="50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G30" s="50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H30" s="50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="40">
@@ -2404,7 +2410,7 @@
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="40">
@@ -2429,7 +2435,7 @@
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="40">
@@ -2454,7 +2460,7 @@
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="47">
@@ -2468,7 +2474,7 @@
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="51">
@@ -2492,7 +2498,7 @@
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2561,43 +2567,43 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -2609,10 +2615,10 @@
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" s="52">
         <v>8.9</v>
@@ -2635,10 +2641,10 @@
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D8" s="36">
         <f>IF(OR(C7="",D7=""),"",D7/C7-1)</f>
@@ -2663,10 +2669,10 @@
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="52">
         <v>4.4000000000000004</v>
@@ -2674,10 +2680,10 @@
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" s="54">
         <f>AVERAGE(C9,C7)</f>
@@ -2706,10 +2712,10 @@
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" s="55">
         <v>81</v>
@@ -2732,10 +2738,10 @@
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D12" s="36">
         <f>IF(OR(C11="",D11=""),"",D11/C11-1)</f>
@@ -2760,10 +2766,10 @@
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" s="54">
         <f>C10*C11*12/1000</f>
@@ -2792,10 +2798,10 @@
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="C14" s="57">
         <v>7.2080000000000002</v>
@@ -2803,10 +2809,10 @@
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" s="54">
         <f>C14-C13</f>
@@ -2830,10 +2836,10 @@
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" s="57">
         <v>4.1790000000000003</v>
@@ -2856,10 +2862,10 @@
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" s="59">
         <f>C13+C15+C16</f>
@@ -2888,10 +2894,10 @@
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D18" s="30">
         <f>IF(OR(C17="",D17=""),"",D17/C17-1)</f>
@@ -2916,7 +2922,7 @@
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -2928,10 +2934,10 @@
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C21" s="60">
         <v>43</v>
@@ -2954,10 +2960,10 @@
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C22" s="18">
         <f>2576/C21</f>
@@ -2981,10 +2987,10 @@
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" s="54">
         <f>C21*C22/1000</f>
@@ -3013,10 +3019,10 @@
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C24" s="57">
         <v>1.51</v>
@@ -3039,10 +3045,10 @@
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
       <c r="A25" s="20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C25" s="59">
         <f>C23+C24</f>
@@ -3071,10 +3077,10 @@
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D26" s="30">
         <f>IF(OR(C25="",D25=""),"",D25/C25-1)</f>
@@ -3099,7 +3105,7 @@
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -3111,10 +3117,10 @@
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C29" s="57">
         <v>3.2010000000000001</v>
@@ -3122,19 +3128,19 @@
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C33" s="61">
         <f>ROUND(C17-11.387,3)</f>
@@ -3143,7 +3149,7 @@
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C34" s="61">
         <f>ROUND(C25-4.086,3)</f>
@@ -3152,7 +3158,7 @@
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C35" s="61">
         <f>ROUND(C29-3.201,3)</f>
@@ -3161,7 +3167,7 @@
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C36" s="61">
         <f>ROUND(C17+C25+C29-18.674,3)</f>
@@ -3170,22 +3176,22 @@
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1">
       <c r="A38" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C39" s="62">
         <v>3213</v>
@@ -3200,7 +3206,7 @@
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C40" s="62">
         <v>1849</v>
@@ -3215,7 +3221,7 @@
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1">
       <c r="A41" s="20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C41" s="62">
         <v>5062</v>
@@ -3230,7 +3236,7 @@
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C42" s="62">
         <v>1056</v>
@@ -3245,7 +3251,7 @@
     </row>
     <row r="43" spans="1:5" ht="15" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C43" s="62">
         <v>555</v>
@@ -3260,7 +3266,7 @@
     </row>
     <row r="44" spans="1:5" ht="15" customHeight="1">
       <c r="A44" s="20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C44" s="62">
         <v>1611</v>
@@ -3275,7 +3281,7 @@
     </row>
     <row r="45" spans="1:5" ht="15" customHeight="1">
       <c r="A45" s="20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C45" s="62">
         <v>1465</v>
@@ -3290,7 +3296,7 @@
     </row>
     <row r="46" spans="1:5" ht="15" customHeight="1">
       <c r="A46" s="20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C46" s="62">
         <v>8138</v>
@@ -3305,42 +3311,42 @@
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1">
       <c r="A48" s="20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="15" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="15" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="15" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="15" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="15" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="15" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="15" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="15" customHeight="1">
@@ -3363,34 +3369,34 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
       <c r="A4" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B5" s="23">
         <f>'Revenue Build'!C25</f>
@@ -3411,7 +3417,7 @@
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
       <c r="A6" s="20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B6" s="57">
         <v>-0.65700000000000003</v>
@@ -3429,7 +3435,7 @@
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
       <c r="A7" s="20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B7" s="57">
         <v>0.65300000000000002</v>
@@ -3447,7 +3453,7 @@
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B8" s="54">
         <f>B7-B6</f>
@@ -3468,7 +3474,7 @@
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B9" s="57">
         <v>0.5</v>
@@ -3486,7 +3492,7 @@
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B10" s="57">
         <v>0</v>
@@ -3504,7 +3510,7 @@
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" s="59">
         <f>B8-B9-B10</f>
@@ -3525,7 +3531,7 @@
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B12" s="57">
         <v>0.8</v>
@@ -3543,7 +3549,7 @@
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B13" s="63">
         <f>B11-B12</f>
@@ -3560,7 +3566,7 @@
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B15" s="57">
         <v>3.8319999999999999</v>
@@ -3578,7 +3584,7 @@
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B16" s="57">
         <v>3.004</v>
@@ -3586,24 +3592,24 @@
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1">
       <c r="A18" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1">
       <c r="A19" s="20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B19" s="30">
         <f>B6/B5</f>
@@ -3624,7 +3630,7 @@
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B20" s="36">
         <f>B7/B5</f>
@@ -3645,7 +3651,7 @@
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1">
       <c r="A21" s="20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B21" s="30">
         <f>B11/B5</f>
@@ -3666,7 +3672,7 @@
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B22" s="36">
         <f>B9/B5</f>
@@ -3687,7 +3693,7 @@
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" s="30">
         <f>B15/B5</f>
@@ -3708,7 +3714,7 @@
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B24" s="36">
         <f>(B6+B16)/B5</f>
@@ -3717,22 +3723,22 @@
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1">
       <c r="A26" s="20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1">
@@ -3756,17 +3762,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B4" s="64">
         <v>5.0099999999999999E-2</v>
@@ -3775,7 +3781,7 @@
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B5" s="65">
         <v>0.05</v>
@@ -3784,7 +3790,7 @@
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B6" s="66">
         <f>CHOOSE(Assumptions!$C$3,Assumptions!C26,Assumptions!C34)</f>
@@ -3794,7 +3800,7 @@
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B7" s="67">
         <f>IF(OR(B5="",B6=""),"",B4+B6*B5)</f>
@@ -3803,7 +3809,7 @@
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B8" s="68">
         <v>5.8549999999999998E-2</v>
@@ -3812,7 +3818,7 @@
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B9" s="69">
         <f>IF(Assumptions!C12="","",Assumptions!C12)</f>
@@ -3821,7 +3827,7 @@
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B10" s="67">
         <f>IF(B9="","",B8*(1-B9))</f>
@@ -3830,7 +3836,7 @@
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B11" s="70">
         <f>Assumptions!C17*Assumptions!C18</f>
@@ -3839,7 +3845,7 @@
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B12" s="44">
         <v>39.363999999999997</v>
@@ -3848,7 +3854,7 @@
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1">
       <c r="A13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B13" s="71">
         <f>B11/(B11+B12)</f>
@@ -3857,7 +3863,7 @@
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1">
       <c r="A14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B14" s="71">
         <f>B12/(B11+B12)</f>
@@ -3866,7 +3872,7 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1">
       <c r="A15" s="72" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B15" s="73">
         <f>IF(OR(B7="",B10=""),"",(B7*B13)+(B10*B14))</f>
@@ -3895,36 +3901,36 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" customHeight="1">
       <c r="A1" s="74" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1">
       <c r="A3" s="38" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="76" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B4" s="77">
         <f>Assumptions!C11</f>
@@ -3953,7 +3959,7 @@
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="79">
@@ -3979,7 +3985,7 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="80">
         <f>Assumptions!C6</f>
@@ -4008,7 +4014,7 @@
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="76" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B7" s="81">
         <f t="shared" ref="B7:G7" si="0">B4*B6</f>
@@ -4037,7 +4043,7 @@
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" s="79">
         <f>Assumptions!$C$12</f>
@@ -4066,7 +4072,7 @@
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="76" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B9" s="81">
         <f t="shared" ref="B9:G9" si="1">B7*(1-B8)</f>
@@ -4095,7 +4101,7 @@
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B10" s="81">
         <f>B4*Assumptions!C8</f>
@@ -4124,7 +4130,7 @@
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="76" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B11" s="81">
         <f>-B4*Assumptions!C7</f>
@@ -4153,7 +4159,7 @@
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B12" s="81"/>
       <c r="C12" s="81">
@@ -4179,7 +4185,7 @@
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="72" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B13" s="82">
         <f>B9+B10+B11</f>
@@ -4208,7 +4214,7 @@
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -4232,7 +4238,7 @@
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C16" s="83">
         <f>1/(1+WACC!$B$15)^C15</f>
@@ -4257,7 +4263,7 @@
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1">
       <c r="A17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C17" s="84">
         <f>C13*C16</f>
@@ -4282,7 +4288,7 @@
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="85" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C19" s="76" t="s">
         <v>5</v>
@@ -4293,7 +4299,7 @@
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1">
       <c r="A20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C20" s="84">
         <f>SUM(C17:G17)</f>
@@ -4307,7 +4313,7 @@
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1">
       <c r="A21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C21" s="81">
         <f>(G13*(1+Assumptions!$C$14)/(WACC!$B$15-Assumptions!$C$14))*G16</f>
@@ -4321,7 +4327,7 @@
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C22" s="81">
         <f>C20+C21</f>
@@ -4335,7 +4341,7 @@
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1">
       <c r="A23" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C23" s="86">
         <f>Assumptions!$C$16</f>
@@ -4349,7 +4355,7 @@
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1">
       <c r="A24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="81">
         <f>C22+C23</f>
@@ -4363,7 +4369,7 @@
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1">
       <c r="A25" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C25" s="88">
         <f>Assumptions!$C$17</f>
@@ -4377,7 +4383,7 @@
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1">
       <c r="A26" s="109" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C26" s="89">
         <f>C24/C25</f>
@@ -4391,7 +4397,7 @@
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1">
       <c r="A27" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C27" s="91">
         <f>Assumptions!$C$18</f>
@@ -4405,7 +4411,7 @@
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1">
       <c r="A28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C28" s="92">
         <f>(C26/C27)-1</f>
@@ -4419,12 +4425,12 @@
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1">
       <c r="A30" s="93" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1">
       <c r="A31" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C31" s="94">
         <f>G13*(1+Assumptions!$C$14)/(WACC!$B$15-Assumptions!$C$14)</f>
@@ -4433,7 +4439,7 @@
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C32" s="94">
         <f>(G7+G10)*Assumptions!$C$15</f>
@@ -4442,7 +4448,7 @@
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1">
       <c r="A33" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C33" s="95">
         <f>C31/(G7+G10)</f>
@@ -4451,7 +4457,7 @@
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1">
       <c r="A34" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C34" s="96">
         <f>(C32*WACC!$B$15-G13)/(G13+C32)</f>
@@ -4460,12 +4466,12 @@
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1">
       <c r="A36" s="93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" customHeight="1">
       <c r="A37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C37" s="97">
         <v>0.09</v>
@@ -4764,12 +4770,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4778,14 +4778,20 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{862344BD-F3B1-4D89-8B3A-825AE27D5BAB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02B5945E-148A-4CB3-9BC2-A5CE3BC4FA9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF393347-CAFE-4A87-9C84-8AC00D6D3B51}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF393347-CAFE-4A87-9C84-8AC00D6D3B51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02B5945E-148A-4CB3-9BC2-A5CE3BC4FA9C}"/>
 </file>